--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486372_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486372_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1317</v>
+        <v>4.7214</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7819</v>
+        <v>4.2483</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3498</v>
+        <v>0.4731</v>
       </c>
       <c r="G2" t="n">
         <v>3.1967</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.3725</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0707</v>
+        <v>0.5372</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2879</v>
+        <v>-0.1646</v>
       </c>
       <c r="V2" t="n">
         <v>0.9347</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2925</v>
+        <v>4.2427</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7913</v>
+        <v>4.7106</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4987</v>
+        <v>-0.4679</v>
       </c>
       <c r="G3" t="n">
         <v>5.9915</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0.0766</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6128</v>
+        <v>0.3064</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2607</v>
+        <v>-0.2298</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9554</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5851</v>
+        <v>1.7978</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6765</v>
+        <v>1.7069</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9085</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2887</v>
+        <v>-1.0219</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2923</v>
+        <v>-1.3167</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.581</v>
+        <v>0.2948</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4399</v>
+        <v>0.3067</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5602</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8797</v>
+        <v>0.8415</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7285</v>
+        <v>-1.3285</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2679</v>
+        <v>-0.7819</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4607</v>
+        <v>-0.5467</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0483</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9337</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1146</v>
+        <v>-0.3206</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3904</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3904</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5914</v>
+        <v>1.7442</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3463</v>
+        <v>1.298</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2451</v>
+        <v>0.4462</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0219</v>
+        <v>-0.2887</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3167</v>
+        <v>0.2923</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2948</v>
+        <v>-0.581</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3067</v>
+        <v>1.4399</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5348000000000001</v>
+        <v>0.5602</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8415</v>
+        <v>0.8797</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3285</v>
+        <v>-1.7285</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7819</v>
+        <v>-0.2679</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5467</v>
+        <v>-1.4607</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3082</v>
+        <v>1.2074</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4747</v>
+        <v>0.5552</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1665</v>
+        <v>0.6522</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. THRASTARSON</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5512</v>
+        <v>-0.1511</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9487</v>
+        <v>0.7096</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4999</v>
+        <v>-0.8607</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.524</v>
+        <v>-1.8398</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0977</v>
+        <v>0.079</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4263</v>
+        <v>-1.9188</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8286</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0492</v>
+        <v>1.0585</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7794</v>
+        <v>-1.0494</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.3526</v>
+        <v>-1.8488</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1468</v>
+        <v>-0.9794</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2057</v>
+        <v>-0.8694</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0702</v>
+        <v>0.3836</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8172</v>
+        <v>0.7006</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8873</v>
+        <v>-0.317</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>S. THRASTARSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.2545</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1833</v>
+        <v>2.0604</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7907</v>
+        <v>-2.3149</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.2981</v>
+        <v>-1.524</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1162</v>
+        <v>-1.0977</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1818</v>
+        <v>-0.4263</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4643</v>
+        <v>1.8286</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6173</v>
+        <v>0.0492</v>
       </c>
       <c r="L7" t="n">
-        <v>0.153</v>
+        <v>1.7794</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8337</v>
+        <v>-3.3526</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4989</v>
+        <v>-1.1468</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3348</v>
+        <v>-2.2057</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3002</v>
+        <v>0.2265</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3447</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9555</v>
+        <v>-0.7024</v>
       </c>
       <c r="V7" t="n">
         <v>0.3904</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6318</v>
+        <v>-0.7638</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4218</v>
+        <v>-0.8003</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.21</v>
+        <v>0.0366</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4163</v>
@@ -1078,13 +1078,13 @@
         <v>2.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3495</v>
+        <v>0.2175</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4132</v>
+        <v>1.0347</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0638</v>
+        <v>-0.8172</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5649999999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0144</v>
+        <v>-1.6855</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1844</v>
+        <v>-0.026</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8299</v>
+        <v>-1.6596</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8398</v>
+        <v>-1.8354</v>
       </c>
       <c r="H9" t="n">
-        <v>0.079</v>
+        <v>-0.4927</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9188</v>
+        <v>-1.3427</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0585</v>
+        <v>0.0547</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0494</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8488</v>
+        <v>-1.9284</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9794</v>
+        <v>-0.5475</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8694</v>
+        <v>-1.381</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4796</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1935</v>
+        <v>-0.119</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2861</v>
+        <v>0.0514</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9399</v>
+        <v>-1.8222</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2495</v>
+        <v>-0.754</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6904</v>
+        <v>-1.0682</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8354</v>
+        <v>-3.2981</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4927</v>
+        <v>-1.1162</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3427</v>
+        <v>-2.1818</v>
       </c>
       <c r="J10" t="n">
-        <v>0.093</v>
+        <v>-0.4643</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0547</v>
+        <v>-0.6173</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0382</v>
+        <v>0.153</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9284</v>
+        <v>-2.8337</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5475</v>
+        <v>-0.4989</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.381</v>
+        <v>-2.3348</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3219</v>
+        <v>1.0854</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3425</v>
+        <v>0.4074</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0205</v>
+        <v>0.678</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4441</v>
+        <v>-1.8507</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.958</v>
+        <v>-0.7345</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4861</v>
+        <v>-1.1162</v>
       </c>
       <c r="G11" t="n">
         <v>-5.2979</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2088</v>
+        <v>0.3845</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8172</v>
+        <v>1.0407</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.026</v>
+        <v>-0.6561</v>
       </c>
       <c r="V11" t="n">
         <v>4.1501</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1359</v>
+        <v>-6.0173</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1819</v>
+        <v>-3.0017</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.954</v>
+        <v>-3.0156</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2438</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1096</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.411</v>
+        <v>-0.2307</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3014</v>
+        <v>0.2397</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2599</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7240000000000011</v>
+        <v>-0.03900000000000059</v>
       </c>
       <c r="E13" t="n">
-        <v>8.7324</v>
+        <v>9.417299999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-9.456300000000001</v>
@@ -1435,19 +1435,19 @@
         <v>-8.5777</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.963699999999999</v>
+        <v>-2.9637</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.614</v>
+        <v>-5.614000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>11.979</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6078</v>
+        <v>3.607799999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>8.371199999999998</v>
+        <v>8.3712</v>
       </c>
       <c r="M13" t="n">
         <v>-20.5564</v>
@@ -1468,19 +1468,19 @@
         <v>16.313</v>
       </c>
       <c r="S13" t="n">
-        <v>3.725399999999999</v>
+        <v>4.41</v>
       </c>
       <c r="T13" t="n">
-        <v>5.311599999999999</v>
+        <v>5.9966</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5863</v>
+        <v>-1.5864</v>
       </c>
       <c r="V13" t="n">
         <v>3.0407</v>
       </c>
       <c r="W13" t="n">
-        <v>6.667199999999999</v>
+        <v>6.6672</v>
       </c>
       <c r="X13" t="n">
         <v>-3.6265</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4153</v>
+        <v>3.8643</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2411</v>
+        <v>5.8891</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8257</v>
+        <v>-2.0248</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8287</v>
+        <v>7.0249</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4772</v>
+        <v>1.3441</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3515</v>
+        <v>5.6808</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8363</v>
+        <v>8.7043</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5324</v>
+        <v>1.8162</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3039</v>
+        <v>6.8881</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0075</v>
+        <v>-1.6793</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0552</v>
+        <v>-0.4721</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9523</v>
+        <v>-1.2073</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6525</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7401</v>
+        <v>2.6101</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6511</v>
+        <v>-0.5083</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4923</v>
+        <v>0.405</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.9133</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.717</v>
+        <v>-0.9123</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.717</v>
+        <v>-2.0422</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5264</v>
+        <v>3.1115</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3303</v>
+        <v>4.7882</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8039</v>
+        <v>-1.6767</v>
       </c>
       <c r="G15" t="n">
-        <v>7.0249</v>
+        <v>2.8287</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3441</v>
+        <v>0.4772</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6808</v>
+        <v>2.3515</v>
       </c>
       <c r="J15" t="n">
-        <v>8.7043</v>
+        <v>4.8363</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8162</v>
+        <v>0.5324</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8881</v>
+        <v>4.3039</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6793</v>
+        <v>-2.0075</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4721</v>
+        <v>-0.0552</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2073</v>
+        <v>-1.9523</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6101</v>
+        <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8462</v>
+        <v>0.3473</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1538</v>
+        <v>1.0395</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6924</v>
+        <v>-0.6922</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9123</v>
+        <v>-0.717</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.0422</v>
+        <v>-0.717</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4044</v>
+        <v>1.5778</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5136</v>
+        <v>1.6254</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1092</v>
+        <v>-0.0476</v>
       </c>
       <c r="G16" t="n">
         <v>2.3138</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9094</v>
+        <v>-0.736</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.293</v>
+        <v>-0.2313</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0094</v>
+        <v>-0.1405</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0042</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0137</v>
+        <v>-0.9212</v>
       </c>
       <c r="G17" t="n">
         <v>1.6739</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2929</v>
+        <v>-0.4239</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1971</v>
+        <v>-0.0264</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4899</v>
+        <v>-0.3975</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9554</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4876</v>
+        <v>-0.3513</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5327</v>
+        <v>-0.1095</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0203</v>
+        <v>-0.2419</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6202</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8728</v>
+        <v>0.3587</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7474</v>
+        <v>-0.3665</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.067</v>
+        <v>1.1278</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7205</v>
+        <v>1.241</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6535</v>
+        <v>-0.1131</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5532</v>
+        <v>-1.1357</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1523</v>
+        <v>-0.8823</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4009</v>
+        <v>-0.2534</v>
       </c>
       <c r="P18" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0204</v>
+        <v>-0.9737</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5997</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6201</v>
+        <v>-0.2382</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.152</v>
+        <v>0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.152</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6057</v>
+        <v>-0.5147</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.333</v>
+        <v>0.1974</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2727</v>
+        <v>-0.7121</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-1.6202</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3587</v>
+        <v>-0.8728</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3665</v>
+        <v>-0.7474</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1278</v>
+        <v>-0.067</v>
       </c>
       <c r="K19" t="n">
-        <v>1.241</v>
+        <v>-0.7205</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1131</v>
+        <v>0.6535</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1357</v>
+        <v>-1.5532</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8823</v>
+        <v>-0.1523</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2534</v>
+        <v>-1.4009</v>
       </c>
       <c r="P19" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.228</v>
+        <v>-0.0475</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9589</v>
+        <v>0.2644</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2691</v>
+        <v>-0.3118</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1952</v>
+        <v>-0.152</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3904</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0942</v>
+        <v>-1.1494</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0964</v>
+        <v>-1.2081</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0022</v>
+        <v>0.0587</v>
       </c>
       <c r="G20" t="n">
         <v>-2.987</v>
@@ -2014,13 +2014,13 @@
         <v>2.6101</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1318</v>
+        <v>0.0766</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7282</v>
+        <v>0.6165</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5964</v>
+        <v>-0.5399</v>
       </c>
       <c r="V20" t="n">
         <v>0.2384</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2799</v>
+        <v>-2.2044</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8519</v>
+        <v>-3.1352</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1318</v>
+        <v>0.9308</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6211</v>
+        <v>-1.2697</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.5143</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2415</v>
+        <v>-0.7554</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3266</v>
+        <v>-0.3562</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4292</v>
+        <v>-0.7236</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8974</v>
+        <v>0.3674</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7056</v>
+        <v>-0.9135</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0497</v>
+        <v>0.2093</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6558</v>
+        <v>-1.1228</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9576</v>
+        <v>-0.87</v>
       </c>
       <c r="Q21" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.2617</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4627</v>
+        <v>0.2884</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4713</v>
+        <v>-0.5501</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9347</v>
+        <v>0.197</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2599</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1453</v>
+        <v>-2.7243</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.588</v>
+        <v>0.6284</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4428</v>
+        <v>-3.3527</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2697</v>
+        <v>0.6211</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5143</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7554</v>
+        <v>1.2415</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3562</v>
+        <v>2.3266</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7236</v>
+        <v>0.4292</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3674</v>
+        <v>1.8974</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9135</v>
+        <v>-1.7056</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2093</v>
+        <v>-1.0497</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1228</v>
+        <v>-0.6558</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2026</v>
+        <v>-0.453</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1644</v>
+        <v>0.2392</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0382</v>
+        <v>-0.6922</v>
       </c>
       <c r="V22" t="n">
-        <v>0.197</v>
+        <v>-0.9347</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0018</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7240000000000002</v>
+        <v>1.469</v>
       </c>
       <c r="E23" t="n">
-        <v>9.456400000000002</v>
+        <v>9.456399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.7323</v>
+        <v>-7.987500000000001</v>
       </c>
       <c r="G23" t="n">
         <v>8.5776</v>
@@ -2248,13 +2248,13 @@
         <v>15.2254</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.7253</v>
+        <v>-2.9802</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5864</v>
+        <v>1.5865</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.311599999999999</v>
+        <v>-4.5665</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0408</v>
